--- a/resampling/input/accessibility_reports_generated/IMC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/IMC_accessibility_report.xlsx
@@ -184,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q34" headerRowCount="1">
-  <autoFilter ref="A1:Q34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q70" headerRowCount="1">
+  <autoFilter ref="A1:Q70"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -210,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O70" headerRowCount="1">
-  <autoFilter ref="A1:O70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O66" headerRowCount="1">
+  <autoFilter ref="A1:O66"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 33 wards, 69 clusters</t>
+          <t>Assigned to you: 69 wards, 65 clusters</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -849,13 +849,13 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -888,11 +888,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Askira/Uba</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
@@ -900,7 +908,7 @@
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -923,29 +931,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Mboakura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Mbokura</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -968,29 +984,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kautikari</t>
+          <t>Ngohi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kautikari</t>
+          <t>Shirarkir</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Askira/Uba; Hawul</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1013,7 +1037,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Korongillum</t>
+          <t>Ngulde</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1023,19 +1047,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Askira/Uba; Biu; Damboa; Hawul</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1058,12 +1090,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pemi</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pemi</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1074,13 +1106,13 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1103,12 +1135,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shikarkir</t>
+          <t>Likama</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Shirarkir</t>
+          <t>Likama</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1125,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1148,29 +1180,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kuburmbulla</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Kuburmbula</t>
-        </is>
-      </c>
+          <t>Azir Multe</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Biu; Damboa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1193,37 +1229,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azir Multe</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Korongilum</t>
-        </is>
-      </c>
+          <t>Gatamarwa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Biu; Damboa</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1246,29 +1270,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gatamarwa</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Gatamarwa</t>
-        </is>
-      </c>
+          <t>Gumsuri</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1291,29 +1319,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Likama</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Likama</t>
-        </is>
-      </c>
+          <t>Hausari Zadawa</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Askira/Uba</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1331,34 +1363,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Damboa</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Damboa Central</t>
-        </is>
-      </c>
+          <t>Kautikari</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Askira/Uba; Damboa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1376,19 +1412,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Gumsuri</t>
-        </is>
-      </c>
+          <t>Korongillum</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>No</t>
@@ -1397,13 +1429,13 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1421,42 +1453,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azir Multe</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nzuda Wuyaram</t>
-        </is>
-      </c>
+          <t>Kuburmbulla</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Biu; Chibok</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1474,34 +1494,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nzuba Wayaram</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nzuda Wuyaram</t>
-        </is>
-      </c>
+          <t>Mussa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Askira/Uba</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1519,34 +1543,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nzuba Wayaram</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Damboa</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ajigin A</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Ajigin A</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1564,42 +1592,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Buratai</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ajigin A</t>
-        </is>
-      </c>
+          <t>Pemi</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Biu</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1617,42 +1633,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dille Huyim</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Mulgo Kopchi</t>
-        </is>
-      </c>
+          <t>Shikarkir</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Askira/Uba</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1675,29 +1679,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wawa Korede</t>
+          <t>Gumsuri</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wawa Korode</t>
+          <t>Gumsuri</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1710,35 +1722,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Galadima B</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Kafa Mafi</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kafa Mafi</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kaga</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1751,35 +1775,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rimaye</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Bego Yerwa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bego</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1792,35 +1828,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kafin Soli</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Damboa Central</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1833,20 +1881,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Galadima A</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Ajigin B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ajigin B</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>No</t>
@@ -1858,10 +1910,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1874,35 +1926,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kunduru Gyaza</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Bita Izge</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mulgo Kopchi</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bama; Gwoza; Konduga</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1915,35 +1979,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fakuwa Kafin Dangi</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Mulgoi Kobchi</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mulgo Kopchi</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1956,17 +2032,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tafashiya Nasarawa</t>
+          <t>Ajigin A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1978,13 +2054,13 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1997,35 +2073,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gachi</t>
+          <t>Azir Multe</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Biu; Chibok</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2038,35 +2122,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sukuntuni</t>
+          <t>Buni Gari</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Biu</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2079,17 +2171,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tama</t>
+          <t>Buratai</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2100,7 +2192,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bindawa</t>
+          <t>Biu</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2109,13 +2201,13 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2128,17 +2220,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Majen Wayya</t>
+          <t>Dalwa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2149,7 +2241,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Charanchi</t>
+          <t>Jere; Konduga</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2158,13 +2250,13 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2177,35 +2269,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tsa Magam</t>
+          <t>Dille Huyim</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Askira/Uba</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2218,17 +2318,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tsakatsa</t>
+          <t>Foi</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2239,7 +2339,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Charanchi; Dutsin-Ma</t>
+          <t>Kaga; Konduga</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2248,13 +2348,13 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2267,17 +2367,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kofa</t>
+          <t>Goneri</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2288,7 +2388,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kusada</t>
+          <t>Kaga</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2297,7 +2397,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2313,23 +2413,1755 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Gur</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Biu</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="10" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Kautikari</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Askira/Uba; Chibok</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Mallumdunari</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="10" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mboakura</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="10" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ngulde</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Askira/Uba; Biu; Chibok; Hawul</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="10" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ngurthavu Kopa</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Askira/Uba</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="10" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Nzuba Wayaram</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="10" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Shetimare</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kaga</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="10" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Wawa Korede</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="10" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fakuwa Kafin Dangi</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Bindawa; Charanchi</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>7</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>25</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="10" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Galadima B</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kusada</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>20</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" s="10" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Gachi</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kusada</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>18</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" s="10" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tafashiya Nasarawa</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>18</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" s="10" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Galadima A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" s="10" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Kafin Soli</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>4</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" s="10" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Boko</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kusada</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" s="10" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Yashe B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kusada</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" s="10" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Doka</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Bindawa; Charanchi; Danja; Rimi</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" s="10" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Duddunni</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Bindawa; Kusada</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" s="10" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Gaiwa</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Bindawa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" s="10" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Garu</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Musawa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" s="10" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Kamri</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Bindawa; Charanchi</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" s="10" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Karaduwa</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Matazu; Musawa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" s="10" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Koda</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="10" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Kofa</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kusada</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" s="10" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Kuki A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Charanchi; Dutsin-Ma; Matazu</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" s="10" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Kunduru Gyaza</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Charanchi; Dutsin-Ma; Matazu</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" s="10" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Majen Wayya</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" s="10" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Radda</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Charanchi; Dutsin-Ma</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" s="10" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Rimaye</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kusada; Musawa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" s="10" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sukuntuni</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Matazu; Musawa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="10" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tama</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Bindawa; Ingawa; Kusada</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="10" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tsa Magam</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Kusada; Matazu</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" s="10" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tsakatsa</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Charanchi; Dutsin-Ma</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" s="10" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Yankamaye</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Kusada</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" s="10" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="O2:O70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2345,7 +4177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2455,7 +4287,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Korongillum</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2465,7 +4297,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>idp_NG008006_1</t>
+          <t>idp_NG008006_10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2504,7 +4336,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Mbalala</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2514,7 +4346,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>idp_NG008006_10</t>
+          <t>idp_NG008006_11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2524,12 +4356,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -2553,7 +4385,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mbalala</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2563,7 +4395,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>idp_NG008006_11</t>
+          <t>idp_NG008006_13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2573,12 +4405,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -2602,7 +4434,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Mbalala</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2612,7 +4444,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>idp_NG008006_13</t>
+          <t>idp_NG008006_14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2651,7 +4483,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mbalala</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2661,7 +4493,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>idp_NG008006_14</t>
+          <t>idp_NG008006_3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2700,7 +4532,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pemi</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2710,7 +4542,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>idp_NG008006_15</t>
+          <t>idp_NG008006_4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2720,12 +4552,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2749,7 +4581,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kuburmbulla</t>
+          <t>Mboakura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2759,7 +4591,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>idp_NG008006_16</t>
+          <t>idp_NG008006_supp1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2798,7 +4630,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kautikari</t>
+          <t>Mboakura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2808,7 +4640,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>idp_NG008006_17</t>
+          <t>idp_NG008006_supp2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2857,7 +4689,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>idp_NG008006_2</t>
+          <t>idp_NG008006_supp3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2906,7 +4738,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>idp_NG008006_3</t>
+          <t>idp_NG008006_supp4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2945,32 +4777,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Whuntaku</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>idp_NG008006_4</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_12</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2994,7 +4822,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kuburmbulla</t>
+          <t>Mbalala</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3004,7 +4832,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_1</t>
+          <t>non_idp_NG008006_13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3049,7 +4877,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_11</t>
+          <t>non_idp_NG008006_14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3084,7 +4912,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3094,18 +4922,18 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_12</t>
+          <t>non_idp_NG008006_8</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -3129,7 +4957,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mbalala</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3139,7 +4967,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_13</t>
+          <t>non_idp_NG008006_supp10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -3174,7 +5002,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mbalala</t>
+          <t>Ngohi</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3184,7 +5012,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_14</t>
+          <t>non_idp_NG008006_supp11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -3219,7 +5047,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kautikari</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3229,7 +5057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_15</t>
+          <t>non_idp_NG008006_supp2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3264,7 +5092,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pemi</t>
+          <t>Mbalala</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3274,7 +5102,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_16</t>
+          <t>non_idp_NG008006_supp3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3309,7 +5137,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kautikari</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3319,7 +5147,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_17</t>
+          <t>non_idp_NG008006_supp4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3354,7 +5182,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azir Multe</t>
+          <t>Mbalala</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3364,7 +5192,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_2</t>
+          <t>non_idp_NG008006_supp5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -3399,7 +5227,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Korongillum</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3409,7 +5237,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_3</t>
+          <t>non_idp_NG008006_supp6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -3444,7 +5272,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Korongillum</t>
+          <t>Likama</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3454,7 +5282,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_4</t>
+          <t>non_idp_NG008006_supp7</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -3489,7 +5317,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shikarkir</t>
+          <t>Ngohi</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3499,7 +5327,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_5</t>
+          <t>non_idp_NG008006_supp8</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -3534,7 +5362,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shikarkir</t>
+          <t>Ngulde</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3544,7 +5372,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_6</t>
+          <t>non_idp_NG008006_supp9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -3574,33 +5402,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chibok</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mbalala</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_7</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>idp_NG008007_13</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3619,33 +5451,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chibok</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Gumsuri</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_8</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>idp_NG008007_15</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3664,25 +5500,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chibok</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gatamarwa</t>
+          <t>Gumsuri</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>idp_NG008007_16</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>6</t>
@@ -3714,7 +5554,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azir Multe</t>
+          <t>Gumsuri</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3724,7 +5564,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>idp_NG008007_1</t>
+          <t>idp_NG008007_17</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3763,7 +5603,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nzuba Wayaram</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3773,7 +5613,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>idp_NG008007_12</t>
+          <t>idp_NG008007_4</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3783,12 +5623,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3822,22 +5662,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>idp_NG008007_13</t>
+          <t>idp_NG008007_supp2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>In-host</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3866,19 +5706,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>idp_NG008007_15</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_13</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>6</t>
@@ -3910,24 +5746,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>idp_NG008007_16</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_7</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>6</t>
@@ -3959,32 +5791,28 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>idp_NG008007_17</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_8</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4008,24 +5836,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azir Multe</t>
+          <t>Kafa Mafi</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>idp_NG008007_2</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_supp1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>6</t>
@@ -4057,24 +5881,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nzuba Wayaram</t>
+          <t>Ajigin B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>idp_NG008007_3</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>In-camp</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_supp10</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>6</t>
@@ -4106,32 +5926,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Gumsuri</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>idp_NG008007_4</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_supp12</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4155,7 +5971,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ajigin A</t>
+          <t>Kafa Mafi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4165,7 +5981,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_1</t>
+          <t>non_idp_NG008007_supp13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -4210,7 +6026,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_13</t>
+          <t>non_idp_NG008007_supp2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -4245,7 +6061,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Mulgoi Kobchi</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4255,7 +6071,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_14</t>
+          <t>non_idp_NG008007_supp3</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -4300,7 +6116,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_15</t>
+          <t>non_idp_NG008007_supp4</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -4335,7 +6151,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dille Huyim</t>
+          <t>Bego Yerwa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4345,7 +6161,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_16</t>
+          <t>non_idp_NG008007_supp5</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -4380,7 +6196,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Buratai</t>
+          <t>Bita Izge</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4390,7 +6206,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_17</t>
+          <t>non_idp_NG008007_supp6</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -4425,7 +6241,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azir Multe</t>
+          <t>Gumsuri</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4435,7 +6251,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_2</t>
+          <t>non_idp_NG008007_supp7</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -4470,7 +6286,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wawa Korede</t>
+          <t>Bego Yerwa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4480,7 +6296,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_3</t>
+          <t>non_idp_NG008007_supp9</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -4505,38 +6321,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Kankia</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azir Multe</t>
+          <t>Kafin Soli</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_4</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>idp_NG021020_2</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4550,38 +6370,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Kankia</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Azir Multe</t>
+          <t>Galadima A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_5</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>idp_NG021020_4</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -4595,38 +6419,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Kankia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nzuba Wayaram</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_6</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>idp_NG021020_6</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -4640,30 +6468,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Kankia</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Tafashiya Nasarawa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_7</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>idp_NG021020_supp1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>6</t>
@@ -4685,38 +6517,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Kankia</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_8</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>idp_NG021020_supp2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -4740,7 +6576,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kunduru Gyaza</t>
+          <t>Gachi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4750,7 +6586,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>idp_NG021020_1</t>
+          <t>idp_NG021020_supp3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4789,7 +6625,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rimaye</t>
+          <t>Gachi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4799,7 +6635,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>idp_NG021020_13</t>
+          <t>idp_NG021020_supp4</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4809,12 +6645,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -4838,32 +6674,28 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kafin Soli</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>idp_NG021020_2</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021020_10</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -4887,24 +6719,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Galadima A</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>idp_NG021020_4</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021020_11</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>12</t>
@@ -4936,32 +6764,28 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Fakuwa Kafin Dangi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>idp_NG021020_6</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021020_13</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -4985,7 +6809,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kafin Soli</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4995,7 +6819,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_1</t>
+          <t>non_idp_NG021020_14</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -5030,7 +6854,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Kafin Soli</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5040,7 +6864,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_10</t>
+          <t>non_idp_NG021020_3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -5075,7 +6899,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Tafashiya Nasarawa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5085,7 +6909,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_11</t>
+          <t>non_idp_NG021020_7</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -5130,7 +6954,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_13</t>
+          <t>non_idp_NG021020_supp1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -5165,7 +6989,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Tafashiya Nasarawa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5175,7 +6999,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_14</t>
+          <t>non_idp_NG021020_supp10</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -5210,7 +7034,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rimaye</t>
+          <t>Tafashiya Nasarawa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5220,7 +7044,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_15</t>
+          <t>non_idp_NG021020_supp3</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -5255,7 +7079,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fakuwa Kafin Dangi</t>
+          <t>Yashe B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5265,7 +7089,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_16</t>
+          <t>non_idp_NG021020_supp4</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -5300,7 +7124,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kunduru Gyaza</t>
+          <t>Fakuwa Kafin Dangi</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5310,7 +7134,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_17</t>
+          <t>non_idp_NG021020_supp5</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -5345,7 +7169,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kafin Soli</t>
+          <t>Fakuwa Kafin Dangi</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5355,7 +7179,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_2</t>
+          <t>non_idp_NG021020_supp6</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -5390,7 +7214,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fakuwa Kafin Dangi</t>
+          <t>Boko</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5400,7 +7224,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_3</t>
+          <t>non_idp_NG021020_supp7</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -5435,7 +7259,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kafin Soli</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5445,7 +7269,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_4</t>
+          <t>non_idp_NG021020_supp8</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -5467,203 +7291,23 @@
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Kankia</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Tafashiya Nasarawa</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>non_idp_NG021020_5</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Kankia</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Sukuntuni</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>non_idp_NG021020_6</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" s="10" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Kankia</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Galadima A</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>non_idp_NG021020_7</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Kankia</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Kunduru Gyaza</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>non_idp_NG021020_9</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" s="10" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="M2:M66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5929,13 +7573,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59E79062-7D92-4ACC-880F-A29B374A0C28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9729D389-B6DA-4B22-A02A-CAA8BDEC9532}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{142A4272-05EC-49A4-9E2C-E3A6E0DE3815}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48999AD1-6D8D-477B-8C32-DA79BFC41098}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E1376FB-44CA-42CE-AA27-68D44ADD7EF1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F70E5F94-FF38-4F16-8181-3A3C21F591EB}"/>
 </file>
--- a/resampling/input/accessibility_reports_generated/IMC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/IMC_accessibility_report.xlsx
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -210,24 +211,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O66" headerRowCount="1">
-  <autoFilter ref="A1:O66"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P78" headerRowCount="1">
+  <autoFilter ref="A1:P78"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +555,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 69 wards, 65 clusters</t>
+          <t>Assigned to you: 69 wards, 77 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +582,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +592,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +602,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +612,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +622,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +632,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +642,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -852,10 +864,10 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -905,10 +917,10 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -931,37 +943,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mboakura</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mbokura</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Damboa</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -984,12 +988,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ngohi</t>
+          <t>Mboakura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shirarkir</t>
+          <t>Mbokura</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Askira/Uba; Hawul</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1008,13 +1012,13 @@
         </is>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1037,12 +1041,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ngulde</t>
+          <t>Ngohi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Korongilum</t>
+          <t>Shirarkir</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1052,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Askira/Uba; Biu; Damboa; Hawul</t>
+          <t>Askira/Uba; Hawul</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1061,13 +1065,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1090,12 +1094,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Likama</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Likama</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1106,13 +1110,13 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1135,29 +1139,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Likama</t>
+          <t>Ngulde</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Likama</t>
+          <t>Korongilum</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Askira/Uba; Biu; Damboa; Hawul</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1679,12 +1691,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Damboa Central</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1694,7 +1706,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chibok</t>
+          <t>Konduga</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1703,13 +1715,13 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1732,12 +1744,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kafa Mafi</t>
+          <t>Mulgoi Kobchi</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kafa Mafi</t>
+          <t>Mulgo Kopchi</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1747,7 +1759,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaga</t>
+          <t>Konduga</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1756,13 +1768,13 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1785,12 +1797,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bego Yerwa</t>
+          <t>Kafa Mafi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bego</t>
+          <t>Kafa Mafi</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1800,7 +1812,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Konduga</t>
+          <t>Kaga</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1809,13 +1821,13 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1838,12 +1850,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Bego Yerwa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Damboa Central</t>
+          <t>Bego</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1865,10 +1877,10 @@
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1891,29 +1903,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ajigin B</t>
+          <t>Bita Izge</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ajigin B</t>
+          <t>Mulgo Kopchi</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bama; Gwoza; Konduga</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1936,29 +1956,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bita Izge</t>
+          <t>Ajigin B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mulgo Kopchi</t>
+          <t>Ajigin B</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Bama; Gwoza; Konduga</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -1989,37 +2001,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mulgoi Kobchi</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Mulgo Kopchi</t>
-        </is>
-      </c>
+          <t>Ajigin A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Konduga</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -2042,17 +2042,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ajigin A</t>
+          <t>Azir Multe</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Biu; Chibok</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
@@ -2083,7 +2091,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azir Multe</t>
+          <t>Buni Gari</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2094,7 +2102,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Biu; Chibok</t>
+          <t>Biu</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2132,7 +2140,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Buni Gari</t>
+          <t>Buratai</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2181,7 +2189,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Buratai</t>
+          <t>Dalwa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2192,7 +2200,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Biu</t>
+          <t>Jere; Konduga</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2230,7 +2238,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dalwa</t>
+          <t>Dille Huyim</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2241,7 +2249,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jere; Konduga</t>
+          <t>Askira/Uba</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2279,7 +2287,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dille Huyim</t>
+          <t>Foi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2290,7 +2298,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Askira/Uba</t>
+          <t>Kaga; Konduga</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2328,7 +2336,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Foi</t>
+          <t>Goneri</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2339,7 +2347,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaga; Konduga</t>
+          <t>Kaga</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2377,7 +2385,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Goneri</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2388,7 +2396,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kaga</t>
+          <t>Gwoza</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2426,7 +2434,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Gumsuri</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2437,7 +2445,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gwoza</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2900,7 +2908,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fakuwa Kafin Dangi</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2911,7 +2919,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bindawa; Charanchi</t>
+          <t>Kusada</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2920,13 +2928,13 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2949,7 +2957,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Fakuwa Kafin Dangi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2960,7 +2968,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kusada</t>
+          <t>Bindawa; Charanchi</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2969,13 +2977,13 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -3103,10 +3111,10 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3639,7 +3647,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -4161,7 +4169,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4177,7 +4185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4185,16 +4193,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4225,50 +4234,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -4302,26 +4316,53 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Safe access achieved and planned activities were completed.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4351,26 +4392,53 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location Is accessible; no access constraints reported </t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4400,26 +4468,53 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Safe access achieved and planned activities were completed.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4449,26 +4544,53 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location Is accessible; no access constraints reported </t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4498,26 +4620,53 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Safe access achieved and planned activities were completed.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4547,26 +4696,53 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Safe access achieved and planned activities were completed.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4596,26 +4772,31 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4645,26 +4826,31 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4694,26 +4880,31 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4743,26 +4934,31 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4777,23 +4973,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garu</t>
+          <t>Mbalala</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_12</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>idp_NG008006_supp5</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4801,13 +5001,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4822,23 +5027,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mbalala</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_13</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>idp_NG008006_supp6</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4846,13 +5055,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4867,23 +5081,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mbalala</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_14</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>idp_NG008006_supp7</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4891,13 +5109,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4912,37 +5135,46 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Whuntaku</t>
+          <t>Likama</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_8</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>idp_NG008006_supp8</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4957,23 +5189,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Whuntaku</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp10</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>idp_NG008006_supp9</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4981,13 +5217,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5002,7 +5243,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ngohi</t>
+          <t>Garu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5012,27 +5253,54 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp11</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_12</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Safe access achieved and planned activities were completed.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5047,7 +5315,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Whuntaku</t>
+          <t>Mbalala</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5057,27 +5325,54 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp2</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_13</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location Is accessible; no access constraints reported </t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5102,27 +5397,54 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp3</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_14</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location Is accessible; no access constraints reported </t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5147,27 +5469,54 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp4</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_8</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Safe access achieved and planned activities were completed.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5182,7 +5531,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mbalala</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5192,27 +5541,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp5</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_supp10</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5227,7 +5581,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Whuntaku</t>
+          <t>Ngohi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5237,27 +5591,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp6</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_supp11</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5272,7 +5631,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Likama</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5282,27 +5641,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp7</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_supp2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5317,7 +5681,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ngohi</t>
+          <t>Mbalala</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5327,27 +5691,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp8</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_supp3</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5362,7 +5731,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ngulde</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5372,27 +5741,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG008006_supp9</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008006_supp4</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5402,46 +5776,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Mbalala</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>idp_NG008007_13</t>
+          <t>non_idp_NG008006_supp5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5451,46 +5826,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Whuntaku</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>idp_NG008007_15</t>
+          <t>non_idp_NG008006_supp6</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5500,46 +5876,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Likama</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>idp_NG008007_16</t>
+          <t>non_idp_NG008006_supp7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5549,46 +5926,47 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Ngohi</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>idp_NG008007_17</t>
+          <t>non_idp_NG008006_supp8</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5598,46 +5976,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Chibok</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Damboa</t>
+          <t>Ngulde</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>idp_NG008007_4</t>
+          <t>non_idp_NG008006_supp9</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5662,31 +6041,54 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>idp_NG008007_supp2</t>
+          <t>idp_NG008007_13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>In-camp</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location Is accessible; no access constraints reported </t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5701,37 +6103,64 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_13</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>idp_NG008007_4</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location Is accessible; no access constraints reported </t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5751,32 +6180,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_7</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>idp_NG008007_supp10</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5796,32 +6234,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_8</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>idp_NG008007_supp11</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5836,37 +6283,46 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kafa Mafi</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp1</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>idp_NG008007_supp12</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5881,23 +6337,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ajigin B</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp10</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>idp_NG008007_supp2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5905,13 +6365,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5926,37 +6391,46 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp12</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>idp_NG008007_supp5</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5971,23 +6445,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kafa Mafi</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp13</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>idp_NG008007_supp6</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5995,13 +6473,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6016,37 +6499,46 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp2</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>idp_NG008007_supp7</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6061,37 +6553,46 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mulgoi Kobchi</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp3</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>idp_NG008007_supp8</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6106,37 +6607,46 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp4</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>idp_NG008007_supp9</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6151,7 +6661,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bego Yerwa</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6161,27 +6671,50 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp5</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_7</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location Is accessible; no access constraints reported </t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6196,7 +6729,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bita Izge</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6206,27 +6739,50 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp6</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_8</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location Is accessible; no access constraints reported </t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" s="10" t="n">
+        <v>46254</v>
+      </c>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6241,7 +6797,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gumsuri</t>
+          <t>Kafa Mafi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6251,27 +6807,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp7</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_supp1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6286,7 +6847,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bego Yerwa</t>
+          <t>Ajigin B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6296,385 +6857,397 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>non_idp_NG008007_supp9</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_supp10</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kafin Soli</t>
+          <t>Kafa Mafi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>idp_NG021020_2</t>
+          <t>non_idp_NG008007_supp13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Galadima A</t>
+          <t>Mulgoi Kobchi</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>idp_NG021020_4</t>
+          <t>non_idp_NG008007_supp14</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Kafa Mafi</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>idp_NG021020_6</t>
+          <t>non_idp_NG008007_supp15</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tafashiya Nasarawa</t>
+          <t>Bita Izge</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>idp_NG021020_supp1</t>
+          <t>non_idp_NG008007_supp17</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Bego Yerwa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>idp_NG021020_supp2</t>
+          <t>non_idp_NG008007_supp18</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gachi</t>
+          <t>Mulgoi Kobchi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>idp_NG021020_supp3</t>
+          <t>non_idp_NG008007_supp20</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gachi</t>
+          <t>Mulgoi Kobchi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>idp_NG021020_supp4</t>
+          <t>non_idp_NG008007_supp3</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Bego Yerwa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6684,42 +7257,47 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_10</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_supp5</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Bita Izge</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6729,42 +7307,47 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_11</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_supp6</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kankia</t>
+          <t>Damboa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fakuwa Kafin Dangi</t>
+          <t>Bego Yerwa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6774,27 +7357,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_13</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008007_supp9</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6809,37 +7397,68 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Galadima B</t>
+          <t>Kafin Soli</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_14</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>idp_NG021020_2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Confirmed accessible and completed - IMC email 23/08/2026.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="n">
+        <v>46257</v>
+      </c>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6854,37 +7473,58 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kafin Soli</t>
+          <t>Galadima A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_3</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>idp_NG021020_4</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6899,37 +7539,58 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tafashiya Nasarawa</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_7</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>idp_NG021020_6</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6944,23 +7605,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fakuwa Kafin Dangi</t>
+          <t>Tafashiya Nasarawa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_supp1</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>idp_NG021020_supp1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6968,13 +7633,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6989,23 +7659,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tafashiya Nasarawa</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_supp10</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>idp_NG021020_supp2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7013,13 +7687,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="10" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7034,23 +7713,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tafashiya Nasarawa</t>
+          <t>Gachi</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_supp3</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>idp_NG021020_supp3</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7058,13 +7741,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7079,23 +7767,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Yashe B</t>
+          <t>Gachi</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_supp4</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>idp_NG021020_supp4</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7103,13 +7795,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7124,37 +7821,46 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fakuwa Kafin Dangi</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_supp5</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>idp_NG021020_supp5</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7169,37 +7875,46 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fakuwa Kafin Dangi</t>
+          <t>Galadima A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_supp6</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>idp_NG021020_supp6</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7214,7 +7929,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boko</t>
+          <t>Galadima B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7224,27 +7939,44 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>non_idp_NG021020_supp7</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021020_10</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7269,45 +8001,710 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>non_idp_NG021020_11</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fakuwa Kafin Dangi</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_13</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Galadima B</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_14</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Kafin Soli</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_3</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tafashiya Nasarawa</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_7</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fakuwa Kafin Dangi</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tafashiya Nasarawa</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp10</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tafashiya Nasarawa</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp3</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Yashe B</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp4</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Fakuwa Kafin Dangi</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp5</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Fakuwa Kafin Dangi</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp6</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Boko</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp7</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Galadima B</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>non_idp_NG021020_supp8</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" s="10" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7573,13 +8970,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9729D389-B6DA-4B22-A02A-CAA8BDEC9532}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F32A8577-9E28-4220-99B6-1F0FEEF9659A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48999AD1-6D8D-477B-8C32-DA79BFC41098}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA73615A-538F-4195-9FFF-A34A254EAD71}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F70E5F94-FF38-4F16-8181-3A3C21F591EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A772BFB0-5253-4D6A-B456-EF956CF97775}"/>
 </file>